--- a/BWI/bestwine_output/bestwine_Réunion.xlsx
+++ b/BWI/bestwine_output/bestwine_Réunion.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4228,6 +4228,95 @@
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De Terre Sainte</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De Terre Sainte</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>121910</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Pierre</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Pierre, Canton de Saint-Pierre-2</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>87 Avenue du Président Mitterrand</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>97410</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>lacavedeterresainte@gmail.com</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+262 262 02 32 09</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>83949786400018</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedeterresainte</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacavedeterresainte/</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Réunion.xlsx
+++ b/BWI/bestwine_output/bestwine_Réunion.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4317,6 +4317,103 @@
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>55293</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis, Canton de Saint-Denis-2</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>35 Avenue de la Victoire</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>97400</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>contact@cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+262 262 21 74 03</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>43922198700019</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Pierrick Grasland</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Réunion.xlsx
+++ b/BWI/bestwine_output/bestwine_Réunion.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA38"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4414,6 +4414,103 @@
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>55293</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis, Canton de Saint-Denis-2</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>35 Avenue de la Victoire</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>97400</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>contact@cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>+262 262 21 74 03</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>43922198700019</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Pierrick Grasland</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Réunion.xlsx
+++ b/BWI/bestwine_output/bestwine_Réunion.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4511,6 +4511,103 @@
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>La Cave De La Victoire</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>55293</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Réunion</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Denis, Canton de Saint-Denis-2</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>35 Avenue de la Victoire</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>97400</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>contact@cavedelavictoire.com</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>+262 262 21 74 03</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>43922198700019</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lacavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavedelavictoire/</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Pierrick Grasland</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
